--- a/automation/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/automation/Test Results/Excel/Automation_Test_Report.xlsx
@@ -3660,7 +3660,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>106</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3680,7 +3680,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>208</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3700,7 +3700,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>245</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,7 +3720,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>258</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>157</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3760,7 +3760,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>247</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3780,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>247</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3820,7 +3820,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3840,7 +3840,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>196</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3860,7 +3860,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>106</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,7 +3880,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,7 +3900,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3920,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>97</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3940,7 +3940,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>102</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,7 +3960,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>131</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3980,7 +3980,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>191</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>285</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4020,7 +4020,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>51</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4040,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,7 +4060,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,7 +4080,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>148</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4100,7 +4100,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>125</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4120,7 +4120,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4140,7 +4140,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>102</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4160,7 +4160,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>168</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4200,7 +4200,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>41</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4220,7 +4220,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>96</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4240,7 +4240,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>218</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>181</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4280,7 +4280,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>237</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>93</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,7 +4320,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>237</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>207</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4360,7 +4360,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>210</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4400,7 +4400,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>74</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,7 +4420,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>239</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4440,7 +4440,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>232</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4460,7 +4460,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>213</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4480,7 +4480,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,7 +4500,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4520,7 +4520,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>234</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4540,7 +4540,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>189</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4560,7 +4560,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>91</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4580,7 +4580,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>53</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4600,7 +4600,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>204</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4620,7 +4620,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>121</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4660,7 +4660,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4680,7 +4680,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>129</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4700,7 +4700,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>110</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4720,7 +4720,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4740,7 +4740,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>127</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4800,7 +4800,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>166</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>213</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4880,7 +4880,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,7 +4900,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,7 +4920,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>41</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>204</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>110</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5000,7 +5000,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>137</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5020,7 +5020,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>41</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5060,7 +5060,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>109</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5080,7 +5080,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>263</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5100,7 +5100,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>266</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5120,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5160,7 +5160,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>112</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5180,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>108</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5200,7 +5200,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>252</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5220,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>58</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5240,7 +5240,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>206</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5260,7 +5260,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>289</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5280,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>114</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5320,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>277</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5340,7 +5340,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>211</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5360,7 +5360,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>87</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>227</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5400,7 +5400,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,7 +5420,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5440,7 +5440,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>189</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5460,7 +5460,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>143</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5480,7 +5480,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5500,7 +5500,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5520,7 +5520,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>250</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5540,7 +5540,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>201</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5560,7 +5560,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>106</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5600,7 +5600,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5620,7 +5620,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>263</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5640,7 +5640,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>270</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5660,7 +5660,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>282</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5680,7 +5680,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>197</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5700,7 +5700,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>180</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5740,7 +5740,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>129</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5760,7 +5760,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>226</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5780,7 +5780,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>242</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5800,7 +5800,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5820,7 +5820,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>238</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5840,7 +5840,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>253</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5860,7 +5860,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>68</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5880,7 +5880,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>137</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>259</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5920,7 +5920,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>125</v>
+        <v>216</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5940,7 +5940,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>56</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5960,7 +5960,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>50</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5980,7 +5980,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>51</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6000,7 +6000,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>105</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6020,7 +6020,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>242</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -6040,7 +6040,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>103</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -6060,7 +6060,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>156</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -6080,7 +6080,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6100,7 +6100,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6120,7 +6120,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>142</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6140,7 +6140,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>161</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6160,7 +6160,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>152</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6180,7 +6180,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>108</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,7 +6200,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>99</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,7 +6220,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>170</v>
+        <v>246</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6240,7 +6240,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>227</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6260,7 +6260,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6280,7 +6280,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>46</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6300,7 +6300,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6320,7 +6320,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>201</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6340,7 +6340,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>197</v>
+        <v>157</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6360,7 +6360,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6380,7 +6380,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6400,7 +6400,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6420,7 +6420,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6440,7 +6440,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>244</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>192</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6480,7 +6480,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>275</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,7 +6500,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>100</v>
+        <v>287</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,7 +6520,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,7 +6540,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>255</v>
+        <v>56</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,7 +6560,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>255</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>287</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6600,7 +6600,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>109</v>
+        <v>282</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6620,7 +6620,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>231</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,7 +6640,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6660,7 +6660,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6700,7 +6700,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>227</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>193</v>
+        <v>82</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>208</v>
+        <v>112</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6780,7 +6780,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6800,7 +6800,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>235</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6820,7 +6820,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>177</v>
+        <v>263</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6840,7 +6840,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6860,7 +6860,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>83</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6880,7 +6880,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6900,7 +6900,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>195</v>
+        <v>228</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6920,7 +6920,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6940,7 +6940,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,7 +6960,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>164</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6980,7 +6980,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -7000,7 +7000,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -7020,7 +7020,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -7040,7 +7040,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>87</v>
+        <v>239</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7060,7 +7060,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>198</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -7080,7 +7080,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>67</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7120,7 +7120,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>182</v>
+        <v>144</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>197</v>
+        <v>43</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7160,7 +7160,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>110</v>
+        <v>158</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>188</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7200,7 +7200,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>281</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7240,7 +7240,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7260,7 +7260,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>207</v>
+        <v>129</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>270</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>70</v>
+        <v>264</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7320,7 +7320,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7340,7 +7340,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>117</v>
+        <v>258</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7360,7 +7360,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>202</v>
+        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>218</v>
+        <v>253</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7400,7 +7400,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>88</v>
+        <v>287</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>205</v>
+        <v>283</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7440,7 +7440,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>207</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,7 +7460,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>50</v>
+        <v>275</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7480,7 +7480,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>227</v>
+        <v>96</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>69</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>186</v>
+        <v>133</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7560,7 +7560,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>254</v>
+        <v>74</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>100</v>
+        <v>289</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7600,7 +7600,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>178</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>162</v>
+        <v>45</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7640,7 +7640,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>275</v>
+        <v>46</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,7 +7660,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>211</v>
+        <v>285</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>100</v>
+        <v>236</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>202</v>
+        <v>111</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7720,7 +7720,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>188</v>
+        <v>73</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7740,7 +7740,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>136</v>
+        <v>156</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>155</v>
+        <v>49</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7780,7 +7780,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>244</v>
+        <v>79</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7800,7 +7800,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7820,7 +7820,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>286</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7840,7 +7840,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7860,7 +7860,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>68</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7880,7 +7880,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>92</v>
+        <v>199</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7900,7 +7900,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7920,7 +7920,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>218</v>
+        <v>129</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7940,7 +7940,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>144</v>
+        <v>47</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7960,7 +7960,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>257</v>
+        <v>164</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7980,7 +7980,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>233</v>
+        <v>152</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8000,7 +8000,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>194</v>
+        <v>155</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8020,7 +8020,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>240</v>
+        <v>170</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8040,7 +8040,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>169</v>
+        <v>268</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8060,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>58</v>
+        <v>243</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8080,7 +8080,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>63</v>
+        <v>170</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8100,7 +8100,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>224</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8120,7 +8120,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>283</v>
+        <v>186</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,7 +8140,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8160,7 +8160,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>113</v>
+        <v>178</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,7 +8180,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,7 +8200,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>133</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,7 +8220,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>124</v>
+        <v>183</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8240,7 +8240,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8260,7 +8260,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>51</v>
+        <v>247</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8280,7 +8280,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>196</v>
+        <v>139</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,7 +8300,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>200</v>
+        <v>112</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,7 +8320,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,7 +8340,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>86</v>
+        <v>126</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,7 +8360,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>104</v>
+        <v>169</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,7 +8380,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>264</v>
+        <v>227</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,7 +8400,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>187</v>
+        <v>98</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,7 +8420,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>273</v>
+        <v>134</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8440,7 +8440,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8460,7 +8460,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>234</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,7 +8480,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>229</v>
+        <v>264</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8520,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,7 +8540,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>229</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8560,7 +8560,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8580,7 +8580,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>72</v>
+        <v>236</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8600,7 +8600,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>93</v>
+        <v>196</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>240</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8640,7 +8640,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8660,7 +8660,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8680,7 +8680,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8700,7 +8700,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>218</v>
+        <v>156</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8720,7 +8720,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8740,7 +8740,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>184</v>
+        <v>280</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8760,7 +8760,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8780,7 +8780,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>82</v>
+        <v>223</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8800,7 +8800,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>80</v>
+        <v>188</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8820,7 +8820,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>54</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8840,7 +8840,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8860,7 +8860,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>204</v>
+        <v>137</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8880,7 +8880,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8900,7 +8900,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>288</v>
+        <v>58</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8920,7 +8920,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>257</v>
+        <v>84</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8940,7 +8940,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>183</v>
+        <v>273</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8960,7 +8960,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>60</v>
+        <v>279</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8980,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>126</v>
+        <v>260</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -9000,7 +9000,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>47</v>
+        <v>258</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -9020,7 +9020,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -9040,7 +9040,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>192</v>
+        <v>249</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -9060,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>242</v>
+        <v>202</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -9100,7 +9100,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>154</v>
+        <v>286</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9120,7 +9120,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>77</v>
+        <v>278</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9140,7 +9140,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>262</v>
+        <v>91</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9160,7 +9160,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9180,7 +9180,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9200,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>223</v>
+        <v>127</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9220,7 +9220,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>59</v>
+        <v>259</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9240,7 +9240,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9260,7 +9260,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>256</v>
+        <v>166</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9280,7 +9280,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>195</v>
+        <v>279</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9300,7 +9300,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>268</v>
+        <v>155</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9320,7 +9320,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>221</v>
+        <v>92</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9340,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9360,7 +9360,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>154</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9380,7 +9380,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>229</v>
+        <v>148</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9400,7 +9400,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9420,7 +9420,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>270</v>
+        <v>222</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9440,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9460,7 +9460,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>186</v>
+        <v>264</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9480,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>206</v>
+        <v>247</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9500,7 +9500,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9520,7 +9520,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>147</v>
+        <v>266</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9560,7 +9560,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>57</v>
+        <v>189</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9580,7 +9580,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9600,7 +9600,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>234</v>
+        <v>183</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9620,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>101</v>
+        <v>250</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9640,7 +9640,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>119</v>
+        <v>251</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9660,7 +9660,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>280</v>
+        <v>54</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9680,7 +9680,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9700,7 +9700,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>286</v>
+        <v>145</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9720,7 +9720,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9740,7 +9740,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>171</v>
+        <v>82</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9760,7 +9760,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>178</v>
+        <v>246</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9780,7 +9780,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>201</v>
+        <v>108</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9800,7 +9800,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>121</v>
+        <v>84</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9820,7 +9820,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>277</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9840,7 +9840,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>154</v>
+        <v>178</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9860,7 +9860,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>181</v>
+        <v>57</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9880,7 +9880,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9900,7 +9900,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>249</v>
+        <v>147</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9920,7 +9920,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>252</v>
+        <v>229</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9940,7 +9940,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>286</v>
+        <v>115</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9960,7 +9960,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9980,7 +9980,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>225</v>
+        <v>189</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -10000,7 +10000,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>158</v>
+        <v>196</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -10020,7 +10020,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>248</v>
+        <v>76</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -10040,7 +10040,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>215</v>
+        <v>138</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -10060,7 +10060,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -10080,7 +10080,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>263</v>
+        <v>70</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -10100,7 +10100,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>199</v>
+        <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10120,7 +10120,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>162</v>
+        <v>256</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10160,7 +10160,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>147</v>
+        <v>278</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10180,7 +10180,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>142</v>
+        <v>250</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10200,7 +10200,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>260</v>
+        <v>178</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10220,7 +10220,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>161</v>
+        <v>254</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>238</v>
+        <v>92</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10260,7 +10260,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>197</v>
+        <v>277</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10280,7 +10280,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>178</v>
+        <v>77</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10300,7 +10300,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10320,7 +10320,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10340,7 +10340,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>85</v>
+        <v>256</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10360,7 +10360,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>184</v>
+        <v>56</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10380,7 +10380,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>257</v>
+        <v>179</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10400,7 +10400,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10420,7 +10420,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>126</v>
+        <v>235</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10440,7 +10440,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>201</v>
+        <v>80</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10480,7 +10480,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>95</v>
+        <v>59</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10500,7 +10500,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>238</v>
+        <v>276</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10520,7 +10520,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>130</v>
+        <v>166</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10540,7 +10540,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>263</v>
+        <v>189</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10560,7 +10560,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>162</v>
+        <v>98</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10580,7 +10580,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10600,7 +10600,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>216</v>
+        <v>187</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10620,7 +10620,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>216</v>
+        <v>126</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10640,7 +10640,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>243</v>
+        <v>171</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10660,7 +10660,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10680,7 +10680,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>88</v>
+        <v>185</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10700,7 +10700,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>247</v>
+        <v>188</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10720,7 +10720,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10740,7 +10740,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>113</v>
+        <v>236</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10760,7 +10760,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>140</v>
+        <v>214</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10780,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>66</v>
+        <v>140</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10800,7 +10800,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10820,7 +10820,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>198</v>
+        <v>153</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10840,7 +10840,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>253</v>
+        <v>154</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10860,7 +10860,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10880,7 +10880,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10900,7 +10900,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>82</v>
+        <v>173</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10920,7 +10920,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>239</v>
+        <v>143</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10940,7 +10940,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>164</v>
+        <v>221</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -10960,7 +10960,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>108</v>
+        <v>177</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -10980,7 +10980,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>94</v>
+        <v>214</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -11000,7 +11000,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>98</v>
+        <v>279</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -11020,7 +11020,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>170</v>
+        <v>203</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -11040,7 +11040,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -11060,7 +11060,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -11080,7 +11080,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -11100,7 +11100,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -11120,7 +11120,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>129</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11140,7 +11140,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>262</v>
+        <v>205</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11160,7 +11160,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>106</v>
+        <v>279</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11180,7 +11180,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>125</v>
+        <v>203</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11200,7 +11200,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>229</v>
+        <v>47</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11220,7 +11220,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>67</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11240,7 +11240,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11260,7 +11260,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>286</v>
+        <v>78</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11280,7 +11280,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>263</v>
+        <v>204</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11300,7 +11300,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11320,7 +11320,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11340,7 +11340,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>283</v>
+        <v>168</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11360,7 +11360,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11380,7 +11380,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>135</v>
+        <v>261</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11400,7 +11400,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>203</v>
+        <v>275</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11420,7 +11420,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>183</v>
+        <v>104</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11440,7 +11440,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>210</v>
+        <v>148</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11460,7 +11460,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11480,7 +11480,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>70</v>
+        <v>112</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11500,7 +11500,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11520,7 +11520,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11540,7 +11540,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>134</v>
+        <v>83</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11560,7 +11560,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11580,7 +11580,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>264</v>
+        <v>155</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11600,7 +11600,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>158</v>
+        <v>105</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11620,7 +11620,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>210</v>
+        <v>134</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11640,7 +11640,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>56</v>
+        <v>106</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11660,7 +11660,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11680,7 +11680,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>281</v>
+        <v>215</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11700,7 +11700,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11720,7 +11720,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>188</v>
+        <v>150</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11740,7 +11740,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11760,7 +11760,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>205</v>
+        <v>128</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11780,7 +11780,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>193</v>
+        <v>243</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11800,7 +11800,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>230</v>
+        <v>146</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11820,7 +11820,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11840,7 +11840,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>65</v>
+        <v>169</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11860,7 +11860,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11880,7 +11880,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>65</v>
+        <v>275</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11900,7 +11900,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11920,7 +11920,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>274</v>
+        <v>83</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11940,7 +11940,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>279</v>
+        <v>222</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -11960,7 +11960,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -11980,7 +11980,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>168</v>
+        <v>213</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -12000,7 +12000,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>121</v>
+        <v>90</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -12020,7 +12020,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>195</v>
+        <v>109</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -12040,7 +12040,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -12060,7 +12060,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>143</v>
+        <v>265</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -12080,7 +12080,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>129</v>
+        <v>276</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -12100,7 +12100,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>219</v>
+        <v>99</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -12120,7 +12120,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>190</v>
+        <v>275</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12140,7 +12140,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12160,7 +12160,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12180,7 +12180,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>46</v>
+        <v>157</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12200,7 +12200,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>63</v>
+        <v>198</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12220,7 +12220,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12240,7 +12240,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12260,7 +12260,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>110</v>
+        <v>278</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12280,7 +12280,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12300,7 +12300,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>127</v>
+        <v>192</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12320,7 +12320,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12340,7 +12340,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12360,7 +12360,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>64</v>
+        <v>215</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12380,7 +12380,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>53</v>
+        <v>262</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12400,7 +12400,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>146</v>
+        <v>276</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12420,7 +12420,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>260</v>
+        <v>145</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12440,7 +12440,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>276</v>
+        <v>103</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12460,7 +12460,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12480,7 +12480,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>154</v>
+        <v>210</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12500,7 +12500,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12540,7 +12540,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>166</v>
+        <v>241</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12560,7 +12560,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12580,7 +12580,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>115</v>
+        <v>196</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12600,7 +12600,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>107</v>
+        <v>153</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12620,7 +12620,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12640,7 +12640,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>287</v>
+        <v>75</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12660,7 +12660,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12680,7 +12680,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12700,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12720,7 +12720,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>186</v>
+        <v>130</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12740,7 +12740,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>63</v>
+        <v>287</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12760,7 +12760,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12780,7 +12780,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>168</v>
+        <v>75</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12800,7 +12800,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>197</v>
+        <v>48</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12820,7 +12820,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>182</v>
+        <v>213</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12840,7 +12840,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>203</v>
+        <v>40</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12860,7 +12860,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>239</v>
+        <v>101</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12880,7 +12880,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>164</v>
+        <v>224</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12900,7 +12900,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>276</v>
+        <v>77</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12920,7 +12920,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>134</v>
+        <v>247</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12940,7 +12940,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>52</v>
+        <v>253</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -12960,7 +12960,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>119</v>
+        <v>273</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -12980,7 +12980,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>272</v>
+        <v>175</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -13000,7 +13000,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>104</v>
+        <v>193</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -13020,7 +13020,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -13040,7 +13040,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -13060,7 +13060,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -13080,7 +13080,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>42</v>
+        <v>204</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13120,7 +13120,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>180</v>
+        <v>278</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13140,7 +13140,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>185</v>
+        <v>252</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13160,7 +13160,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>165</v>
+        <v>231</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13180,7 +13180,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13200,7 +13200,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>186</v>
+        <v>92</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13220,7 +13220,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>266</v>
+        <v>48</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13240,7 +13240,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13260,7 +13260,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13280,7 +13280,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>174</v>
+        <v>222</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13300,7 +13300,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13320,7 +13320,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>105</v>
+        <v>193</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13340,7 +13340,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13360,7 +13360,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13380,7 +13380,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>161</v>
+        <v>195</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13400,7 +13400,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>123</v>
+        <v>233</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13420,7 +13420,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>120</v>
+        <v>259</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13440,7 +13440,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>258</v>
+        <v>115</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13460,7 +13460,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>217</v>
+        <v>158</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13480,7 +13480,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>58</v>
+        <v>224</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13500,7 +13500,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13520,7 +13520,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>179</v>
+        <v>121</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13540,7 +13540,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13560,7 +13560,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13580,7 +13580,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>121</v>
+        <v>227</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13600,7 +13600,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>116</v>
+        <v>146</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13620,7 +13620,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>119</v>
+        <v>60</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13640,7 +13640,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -13660,7 +13660,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>275</v>
+        <v>236</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13680,7 +13680,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>192</v>
+        <v>71</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13700,7 +13700,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13720,7 +13720,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -13740,7 +13740,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>267</v>
+        <v>191</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -13760,7 +13760,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>158</v>
+        <v>103</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -13780,7 +13780,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>47</v>
+        <v>260</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13800,7 +13800,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>262</v>
+        <v>175</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13820,7 +13820,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>189</v>
+        <v>52</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -13840,7 +13840,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>94</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -13898,7 +13898,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>106</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -13918,7 +13918,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>208</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -13938,7 +13938,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>245</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -13958,7 +13958,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>258</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -13978,7 +13978,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>157</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -13998,7 +13998,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>247</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -14018,7 +14018,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>247</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14038,7 +14038,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14058,7 +14058,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -14078,7 +14078,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>196</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14098,7 +14098,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>106</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -14118,7 +14118,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -14138,7 +14138,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -14158,7 +14158,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>97</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14178,7 +14178,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>102</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -14198,7 +14198,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>131</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -14218,7 +14218,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>191</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -14238,7 +14238,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>285</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -14258,7 +14258,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>51</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -14278,7 +14278,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -14298,7 +14298,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -14318,7 +14318,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>148</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -14338,7 +14338,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>125</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -14358,7 +14358,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -14378,7 +14378,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>102</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -14398,7 +14398,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>168</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -14418,7 +14418,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>41</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -14458,7 +14458,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>96</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -14478,7 +14478,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>218</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -14498,7 +14498,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>181</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -14518,7 +14518,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>237</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -14538,7 +14538,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>93</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -14558,7 +14558,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>237</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -14578,7 +14578,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>207</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -14598,7 +14598,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -14618,7 +14618,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>210</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -14638,7 +14638,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>74</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -14658,7 +14658,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>239</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -14678,7 +14678,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>232</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -14698,7 +14698,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>213</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -14718,7 +14718,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -14738,7 +14738,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -14758,7 +14758,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>234</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>189</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -14798,7 +14798,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>91</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -14818,7 +14818,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>53</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -14838,7 +14838,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>204</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -14858,7 +14858,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -14878,7 +14878,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>121</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -14898,7 +14898,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -14918,7 +14918,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>129</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -14938,7 +14938,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>110</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -14958,7 +14958,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -14978,7 +14978,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -14998,7 +14998,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -15018,7 +15018,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>127</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -15038,7 +15038,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -15058,7 +15058,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -15078,7 +15078,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>166</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -15098,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>213</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -15118,7 +15118,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -15138,7 +15138,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -15158,7 +15158,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>41</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -15178,7 +15178,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>204</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -15198,7 +15198,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>110</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -15218,7 +15218,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -15238,7 +15238,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>137</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -15258,7 +15258,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -15278,7 +15278,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>41</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -15298,7 +15298,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>109</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -15318,7 +15318,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>263</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -15338,7 +15338,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>266</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -15358,7 +15358,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>170</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -15378,7 +15378,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -15398,7 +15398,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>112</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -15418,7 +15418,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>108</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -15438,7 +15438,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>252</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -15458,7 +15458,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>58</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -15478,7 +15478,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>206</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -15498,7 +15498,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>289</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -15518,7 +15518,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -15538,7 +15538,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>114</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -15558,7 +15558,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>277</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -15578,7 +15578,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>211</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -15598,7 +15598,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>87</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -15618,7 +15618,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>227</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -15638,7 +15638,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -15658,7 +15658,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -15678,7 +15678,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>189</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -15698,7 +15698,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>143</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -15718,7 +15718,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -15738,7 +15738,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -15758,7 +15758,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>250</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -15778,7 +15778,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>201</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15798,7 +15798,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15818,7 +15818,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>106</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15838,7 +15838,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15858,7 +15858,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>263</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -15878,7 +15878,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>270</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -15898,7 +15898,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>282</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -15918,7 +15918,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>197</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -15938,7 +15938,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>180</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -15958,7 +15958,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -15978,7 +15978,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>129</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -15998,7 +15998,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>226</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -16018,7 +16018,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>242</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -16038,7 +16038,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>194</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -16058,7 +16058,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>238</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16078,7 +16078,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>253</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -16098,7 +16098,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>68</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -16118,7 +16118,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>137</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -16138,7 +16138,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>259</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -16158,7 +16158,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>125</v>
+        <v>216</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -16178,7 +16178,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>56</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -16198,7 +16198,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>50</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -16218,7 +16218,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>51</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -16238,7 +16238,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>105</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -16258,7 +16258,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>242</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -16278,7 +16278,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>103</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -16298,7 +16298,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>156</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -16318,7 +16318,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -16338,7 +16338,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -16358,7 +16358,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>142</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -16378,7 +16378,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>161</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -16398,7 +16398,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>152</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -16418,7 +16418,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>108</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -16438,7 +16438,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>99</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -16458,7 +16458,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>170</v>
+        <v>246</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -16478,7 +16478,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>227</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -16498,7 +16498,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -16518,7 +16518,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>46</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -16538,7 +16538,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -16558,7 +16558,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>201</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -16578,7 +16578,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>197</v>
+        <v>157</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -16598,7 +16598,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -16618,7 +16618,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -16638,7 +16638,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -16658,7 +16658,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -16678,7 +16678,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>244</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -16698,7 +16698,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>192</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -16718,7 +16718,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>275</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -16738,7 +16738,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>100</v>
+        <v>287</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -16758,7 +16758,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16778,7 +16778,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>255</v>
+        <v>56</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -16798,7 +16798,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>255</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -16818,7 +16818,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>287</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -16838,7 +16838,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>109</v>
+        <v>282</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -16858,7 +16858,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>231</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -16878,7 +16878,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -16898,7 +16898,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -16918,7 +16918,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -16938,7 +16938,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -16958,7 +16958,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>227</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -16978,7 +16978,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>193</v>
+        <v>82</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -16998,7 +16998,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>208</v>
+        <v>112</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17018,7 +17018,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -17038,7 +17038,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>235</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -17058,7 +17058,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>177</v>
+        <v>263</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -17078,7 +17078,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -17098,7 +17098,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>83</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -17118,7 +17118,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -17138,7 +17138,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>195</v>
+        <v>228</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -17158,7 +17158,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -17178,7 +17178,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -17198,7 +17198,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>164</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -17218,7 +17218,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -17238,7 +17238,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -17258,7 +17258,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -17278,7 +17278,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>87</v>
+        <v>239</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -17298,7 +17298,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>198</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -17318,7 +17318,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -17338,7 +17338,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>67</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -17358,7 +17358,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>182</v>
+        <v>144</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -17378,7 +17378,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>197</v>
+        <v>43</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -17398,7 +17398,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>110</v>
+        <v>158</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -17418,7 +17418,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>188</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -17438,7 +17438,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -17458,7 +17458,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>281</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -17478,7 +17478,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -17498,7 +17498,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>207</v>
+        <v>129</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -17518,7 +17518,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>270</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -17538,7 +17538,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>70</v>
+        <v>264</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -17558,7 +17558,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -17578,7 +17578,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>117</v>
+        <v>258</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -17598,7 +17598,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>202</v>
+        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -17618,7 +17618,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>218</v>
+        <v>253</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -17638,7 +17638,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>88</v>
+        <v>287</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -17658,7 +17658,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>205</v>
+        <v>283</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -17678,7 +17678,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>207</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17698,7 +17698,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>50</v>
+        <v>275</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -17718,7 +17718,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>227</v>
+        <v>96</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -17738,7 +17738,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -17758,7 +17758,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>69</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -17778,7 +17778,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>186</v>
+        <v>133</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -17798,7 +17798,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>254</v>
+        <v>74</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -17818,7 +17818,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>100</v>
+        <v>289</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -17838,7 +17838,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>178</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -17858,7 +17858,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>162</v>
+        <v>45</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -17878,7 +17878,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>275</v>
+        <v>46</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -17898,7 +17898,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>211</v>
+        <v>285</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -17918,7 +17918,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>100</v>
+        <v>236</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -17938,7 +17938,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>202</v>
+        <v>111</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -17958,7 +17958,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>188</v>
+        <v>73</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -17978,7 +17978,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>136</v>
+        <v>156</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -17998,7 +17998,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>155</v>
+        <v>49</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -18018,7 +18018,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>244</v>
+        <v>79</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -18038,7 +18038,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -18058,7 +18058,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>286</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -18078,7 +18078,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -18098,7 +18098,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>68</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -18118,7 +18118,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>92</v>
+        <v>199</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -18138,7 +18138,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -18158,7 +18158,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>218</v>
+        <v>129</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -18178,7 +18178,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>144</v>
+        <v>47</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -18198,7 +18198,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>257</v>
+        <v>164</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -18218,7 +18218,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>233</v>
+        <v>152</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -18238,7 +18238,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>194</v>
+        <v>155</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -18258,7 +18258,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>240</v>
+        <v>170</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -18278,7 +18278,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>169</v>
+        <v>268</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -18298,7 +18298,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>58</v>
+        <v>243</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -18318,7 +18318,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>63</v>
+        <v>170</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -18338,7 +18338,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>224</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -18358,7 +18358,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>283</v>
+        <v>186</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -18378,7 +18378,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -18398,7 +18398,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>113</v>
+        <v>178</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -18418,7 +18418,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -18438,7 +18438,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>133</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -18458,7 +18458,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>124</v>
+        <v>183</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -18478,7 +18478,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -18498,7 +18498,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>51</v>
+        <v>247</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -18518,7 +18518,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>196</v>
+        <v>139</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -18538,7 +18538,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>200</v>
+        <v>112</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -18558,7 +18558,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -18578,7 +18578,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>86</v>
+        <v>126</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -18598,7 +18598,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>104</v>
+        <v>169</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -18618,7 +18618,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>264</v>
+        <v>227</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -18638,7 +18638,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>187</v>
+        <v>98</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -18658,7 +18658,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>273</v>
+        <v>134</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -18678,7 +18678,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -18698,7 +18698,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>234</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -18718,7 +18718,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -18738,7 +18738,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>229</v>
+        <v>264</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -18758,7 +18758,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -18778,7 +18778,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>229</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -18798,7 +18798,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -18818,7 +18818,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>72</v>
+        <v>236</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -18838,7 +18838,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>93</v>
+        <v>196</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -18858,7 +18858,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>240</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -18878,7 +18878,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -18898,7 +18898,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -18918,7 +18918,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -18938,7 +18938,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>218</v>
+        <v>156</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -18958,7 +18958,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -18978,7 +18978,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>184</v>
+        <v>280</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -18998,7 +18998,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -19018,7 +19018,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>82</v>
+        <v>223</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -19038,7 +19038,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>80</v>
+        <v>188</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -19058,7 +19058,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>54</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -19078,7 +19078,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -19098,7 +19098,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>204</v>
+        <v>137</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -19118,7 +19118,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -19138,7 +19138,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>288</v>
+        <v>58</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -19158,7 +19158,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>257</v>
+        <v>84</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -19178,7 +19178,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>183</v>
+        <v>273</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -19198,7 +19198,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>60</v>
+        <v>279</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -19218,7 +19218,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>126</v>
+        <v>260</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -19238,7 +19238,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>47</v>
+        <v>258</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -19258,7 +19258,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -19278,7 +19278,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>192</v>
+        <v>249</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -19298,7 +19298,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -19318,7 +19318,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>242</v>
+        <v>202</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -19338,7 +19338,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>154</v>
+        <v>286</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -19358,7 +19358,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>77</v>
+        <v>278</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -19378,7 +19378,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>262</v>
+        <v>91</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -19398,7 +19398,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -19418,7 +19418,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -19438,7 +19438,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>223</v>
+        <v>127</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -19458,7 +19458,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>59</v>
+        <v>259</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -19478,7 +19478,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -19498,7 +19498,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>256</v>
+        <v>166</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -19518,7 +19518,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>195</v>
+        <v>279</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -19538,7 +19538,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>268</v>
+        <v>155</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -19558,7 +19558,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>221</v>
+        <v>92</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -19578,7 +19578,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -19598,7 +19598,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>154</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -19618,7 +19618,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>229</v>
+        <v>148</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -19638,7 +19638,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>273</v>
+        <v>67</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -19658,7 +19658,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>270</v>
+        <v>222</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -19678,7 +19678,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -19698,7 +19698,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>186</v>
+        <v>264</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -19718,7 +19718,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>206</v>
+        <v>247</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -19738,7 +19738,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -19758,7 +19758,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>147</v>
+        <v>266</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -19778,7 +19778,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -19798,7 +19798,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>57</v>
+        <v>189</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -19818,7 +19818,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -19838,7 +19838,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>234</v>
+        <v>183</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -19858,7 +19858,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>101</v>
+        <v>250</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -19878,7 +19878,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>119</v>
+        <v>251</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -19898,7 +19898,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>280</v>
+        <v>54</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -19918,7 +19918,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -19938,7 +19938,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>286</v>
+        <v>145</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -19958,7 +19958,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -19978,7 +19978,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>171</v>
+        <v>82</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -19998,7 +19998,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>178</v>
+        <v>246</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -20018,7 +20018,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>201</v>
+        <v>108</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -20038,7 +20038,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>121</v>
+        <v>84</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -20058,7 +20058,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>277</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -20078,7 +20078,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>154</v>
+        <v>178</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -20098,7 +20098,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>181</v>
+        <v>57</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -20118,7 +20118,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -20138,7 +20138,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>249</v>
+        <v>147</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -20158,7 +20158,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>252</v>
+        <v>229</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -20178,7 +20178,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>286</v>
+        <v>115</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -20198,7 +20198,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -20218,7 +20218,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>225</v>
+        <v>189</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -20238,7 +20238,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>158</v>
+        <v>196</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -20258,7 +20258,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>248</v>
+        <v>76</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -20278,7 +20278,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>215</v>
+        <v>138</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -20298,7 +20298,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -20318,7 +20318,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>263</v>
+        <v>70</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -20338,7 +20338,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>199</v>
+        <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -20358,7 +20358,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -20378,7 +20378,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>162</v>
+        <v>256</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -20398,7 +20398,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>147</v>
+        <v>278</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -20418,7 +20418,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>142</v>
+        <v>250</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -20438,7 +20438,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>260</v>
+        <v>178</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -20458,7 +20458,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>161</v>
+        <v>254</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -20478,7 +20478,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>238</v>
+        <v>92</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -20498,7 +20498,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>197</v>
+        <v>277</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -20518,7 +20518,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>178</v>
+        <v>77</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -20538,7 +20538,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -20558,7 +20558,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -20578,7 +20578,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>85</v>
+        <v>256</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -20598,7 +20598,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>184</v>
+        <v>56</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -20618,7 +20618,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>257</v>
+        <v>179</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -20638,7 +20638,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -20658,7 +20658,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>126</v>
+        <v>235</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -20678,7 +20678,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -20698,7 +20698,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>201</v>
+        <v>80</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -20718,7 +20718,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>95</v>
+        <v>59</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -20738,7 +20738,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>238</v>
+        <v>276</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -20758,7 +20758,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>130</v>
+        <v>166</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -20778,7 +20778,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>263</v>
+        <v>189</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -20798,7 +20798,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>162</v>
+        <v>98</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -20818,7 +20818,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -20838,7 +20838,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>216</v>
+        <v>187</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -20858,7 +20858,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>216</v>
+        <v>126</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -20878,7 +20878,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>243</v>
+        <v>171</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -20898,7 +20898,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -20918,7 +20918,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>88</v>
+        <v>185</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -20938,7 +20938,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>247</v>
+        <v>188</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -20958,7 +20958,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -20978,7 +20978,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>113</v>
+        <v>236</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -20998,7 +20998,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>140</v>
+        <v>214</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -21018,7 +21018,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>66</v>
+        <v>140</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -21038,7 +21038,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -21058,7 +21058,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>198</v>
+        <v>153</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -21078,7 +21078,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>253</v>
+        <v>154</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -21098,7 +21098,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -21118,7 +21118,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -21138,7 +21138,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>82</v>
+        <v>173</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -21158,7 +21158,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>239</v>
+        <v>143</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -21178,7 +21178,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>164</v>
+        <v>221</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -21198,7 +21198,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>108</v>
+        <v>177</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -21218,7 +21218,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>94</v>
+        <v>214</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -21238,7 +21238,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>98</v>
+        <v>279</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -21258,7 +21258,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>170</v>
+        <v>203</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -21278,7 +21278,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -21298,7 +21298,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -21318,7 +21318,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -21338,7 +21338,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -21358,7 +21358,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>129</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -21378,7 +21378,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>262</v>
+        <v>205</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -21398,7 +21398,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>106</v>
+        <v>279</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -21418,7 +21418,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>125</v>
+        <v>203</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -21438,7 +21438,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>229</v>
+        <v>47</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -21458,7 +21458,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>67</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -21478,7 +21478,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -21498,7 +21498,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>286</v>
+        <v>78</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -21518,7 +21518,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>263</v>
+        <v>204</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -21538,7 +21538,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -21558,7 +21558,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -21578,7 +21578,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>283</v>
+        <v>168</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -21598,7 +21598,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -21618,7 +21618,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>135</v>
+        <v>261</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -21638,7 +21638,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>203</v>
+        <v>275</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -21658,7 +21658,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>183</v>
+        <v>104</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -21678,7 +21678,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>210</v>
+        <v>148</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -21698,7 +21698,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -21718,7 +21718,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>70</v>
+        <v>112</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -21738,7 +21738,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -21758,7 +21758,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -21778,7 +21778,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>134</v>
+        <v>83</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -21798,7 +21798,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -21818,7 +21818,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>264</v>
+        <v>155</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -21838,7 +21838,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>158</v>
+        <v>105</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -21858,7 +21858,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>210</v>
+        <v>134</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -21878,7 +21878,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>56</v>
+        <v>106</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -21898,7 +21898,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -21918,7 +21918,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>281</v>
+        <v>215</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -21938,7 +21938,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -21958,7 +21958,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>188</v>
+        <v>150</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -21978,7 +21978,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -21998,7 +21998,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>205</v>
+        <v>128</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -22018,7 +22018,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>193</v>
+        <v>243</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -22038,7 +22038,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>230</v>
+        <v>146</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22058,7 +22058,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22078,7 +22078,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>65</v>
+        <v>169</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -22098,7 +22098,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -22118,7 +22118,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>65</v>
+        <v>275</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -22138,7 +22138,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -22158,7 +22158,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>274</v>
+        <v>83</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -22178,7 +22178,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>279</v>
+        <v>222</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -22198,7 +22198,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -22218,7 +22218,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>168</v>
+        <v>213</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -22238,7 +22238,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>121</v>
+        <v>90</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -22258,7 +22258,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>195</v>
+        <v>109</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -22278,7 +22278,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -22298,7 +22298,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>143</v>
+        <v>265</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -22318,7 +22318,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>129</v>
+        <v>276</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -22338,7 +22338,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>219</v>
+        <v>99</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -22358,7 +22358,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>190</v>
+        <v>275</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -22378,7 +22378,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -22398,7 +22398,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -22418,7 +22418,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>46</v>
+        <v>157</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -22438,7 +22438,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>63</v>
+        <v>198</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -22458,7 +22458,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -22478,7 +22478,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -22498,7 +22498,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>110</v>
+        <v>278</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -22518,7 +22518,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -22538,7 +22538,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>127</v>
+        <v>192</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -22558,7 +22558,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>202</v>
+        <v>153</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -22578,7 +22578,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -22598,7 +22598,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>64</v>
+        <v>215</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -22618,7 +22618,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>53</v>
+        <v>262</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -22638,7 +22638,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>146</v>
+        <v>276</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -22658,7 +22658,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>260</v>
+        <v>145</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -22678,7 +22678,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>276</v>
+        <v>103</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -22698,7 +22698,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -22718,7 +22718,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>154</v>
+        <v>210</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -22738,7 +22738,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -22758,7 +22758,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -22778,7 +22778,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>166</v>
+        <v>241</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -22798,7 +22798,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -22818,7 +22818,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>115</v>
+        <v>196</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -22838,7 +22838,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>107</v>
+        <v>153</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -22858,7 +22858,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -22878,7 +22878,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>287</v>
+        <v>75</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -22898,7 +22898,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -22918,7 +22918,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>280</v>
+        <v>160</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -22938,7 +22938,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -22958,7 +22958,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>186</v>
+        <v>130</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -22978,7 +22978,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>63</v>
+        <v>287</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -22998,7 +22998,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -23018,7 +23018,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>168</v>
+        <v>75</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -23038,7 +23038,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>197</v>
+        <v>48</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -23058,7 +23058,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>182</v>
+        <v>213</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -23078,7 +23078,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>203</v>
+        <v>40</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -23098,7 +23098,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>239</v>
+        <v>101</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -23118,7 +23118,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>164</v>
+        <v>224</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23138,7 +23138,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>276</v>
+        <v>77</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -23158,7 +23158,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>134</v>
+        <v>247</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -23178,7 +23178,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>52</v>
+        <v>253</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23198,7 +23198,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>119</v>
+        <v>273</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -23218,7 +23218,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>272</v>
+        <v>175</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -23238,7 +23238,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>104</v>
+        <v>193</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -23258,7 +23258,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23278,7 +23278,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -23298,7 +23298,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -23318,7 +23318,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>42</v>
+        <v>204</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -23338,7 +23338,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -23358,7 +23358,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>180</v>
+        <v>278</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -23378,7 +23378,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>185</v>
+        <v>252</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23398,7 +23398,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>165</v>
+        <v>231</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -23418,7 +23418,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23438,7 +23438,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>186</v>
+        <v>92</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -23458,7 +23458,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>266</v>
+        <v>48</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -23478,7 +23478,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -23498,7 +23498,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -23518,7 +23518,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>174</v>
+        <v>222</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -23538,7 +23538,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -23558,7 +23558,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>105</v>
+        <v>193</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -23578,7 +23578,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -23598,7 +23598,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -23618,7 +23618,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>161</v>
+        <v>195</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -23638,7 +23638,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>123</v>
+        <v>233</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -23658,7 +23658,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>120</v>
+        <v>259</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -23678,7 +23678,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>258</v>
+        <v>115</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -23698,7 +23698,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>217</v>
+        <v>158</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -23718,7 +23718,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>58</v>
+        <v>224</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -23738,7 +23738,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -23758,7 +23758,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>179</v>
+        <v>121</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -23778,7 +23778,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -23798,7 +23798,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -23818,7 +23818,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>121</v>
+        <v>227</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -23838,7 +23838,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>116</v>
+        <v>146</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -23858,7 +23858,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>119</v>
+        <v>60</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -23878,7 +23878,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -23898,7 +23898,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>275</v>
+        <v>236</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -23918,7 +23918,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>192</v>
+        <v>71</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -23938,7 +23938,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -23958,7 +23958,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -23978,7 +23978,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>267</v>
+        <v>191</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -23998,7 +23998,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>158</v>
+        <v>103</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -24018,7 +24018,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>47</v>
+        <v>260</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -24038,7 +24038,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>262</v>
+        <v>175</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -24058,7 +24058,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>189</v>
+        <v>52</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -24078,7 +24078,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>94</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
